--- a/custom-colors.xlsx
+++ b/custom-colors.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3642dd6725b5ad82/workspace/cursor/AI_Driven_School/src/personal-visual-explainers/.claude/skills/minutes-maid/references/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3642dd6725b5ad82/workspace/GitHub/AI_Driven_School/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{D331D845-7AF5-4698-92E9-69A34921C840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E7C766D-6E87-4227-89DB-688C736DB6C4}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{D331D845-7AF5-4698-92E9-69A34921C840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{02C603BD-E7DB-4DFF-9A2F-1E2AA22B5D56}"/>
   <bookViews>
-    <workbookView xWindow="7650" yWindow="0" windowWidth="16245" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12555" yWindow="0" windowWidth="16245" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="All" sheetId="8" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="581">
   <si>
     <t>Color</t>
   </si>
@@ -1809,6 +1809,10 @@
   </si>
   <si>
     <t>#00A4FD</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Custom_Blue_50</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2692,10 +2696,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3713,7 +3713,7 @@
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A49" t="s">
-        <v>487</v>
+        <v>580</v>
       </c>
       <c r="B49" t="s">
         <v>414</v>
